--- a/src/assets/templates/template_repasse_icms.xlsx
+++ b/src/assets/templates/template_repasse_icms.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos Andre\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos Andre\Pictures\CRIPTO - DEPLOY ADM VERCEL\frontend-administrador\src\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F938D1F-27FB-4499-99F3-321DB7E449A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421AD30A-2E9B-402E-A165-8264303D37C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Resultado Consulta Repasse dos Municípios</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>TOTAIS</t>
+  </si>
+  <si>
+    <t>ICMS</t>
   </si>
 </sst>
 </file>
@@ -356,6 +359,63 @@
     <xf numFmtId="4" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -369,63 +429,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -717,80 +720,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="23"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="3" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="30"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
@@ -817,8 +822,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -829,10 +834,10 @@
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -844,6 +849,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:B6"/>
@@ -857,11 +867,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
